--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Thematic Advantage Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Thematic Advantage Fund (FOF).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0305453C-E69D-44DA-8C8B-9EE25E8B8921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DA10B4-FBAC-41E6-982F-296F7B84E604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Thematic Advantage Fund (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -82,10 +82,28 @@
     <t>INF109KC1GH2</t>
   </si>
   <si>
-    <t>ICICI Prudential Infrastructure Fund - Direct Plan -  Growth</t>
-  </si>
-  <si>
-    <t>INF109K018M4</t>
+    <t>ICICI Prudential Technology Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109K01Z48</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Ultra Short Term Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109K01T04</t>
+  </si>
+  <si>
+    <t>ICICI Prudential Energy Opportunities Fund - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF109KC12W6</t>
+  </si>
+  <si>
+    <t>ICICI Prudential FMCG Fund - Direct Plan - Growth</t>
+  </si>
+  <si>
+    <t>INF109K01Z14</t>
   </si>
   <si>
     <t>ICICI Prudential Equity Minimum Variance Fund - Direct - Growth</t>
@@ -94,24 +112,6 @@
     <t>INF109KC10Y6</t>
   </si>
   <si>
-    <t>ICICI Prudential Ultra Short Term Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109K01T04</t>
-  </si>
-  <si>
-    <t>ICICI Prudential Housing Opportunities Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF109KC10C2</t>
-  </si>
-  <si>
-    <t>ICICI Prudential FMCG Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF109K01Z14</t>
-  </si>
-  <si>
     <t>TREPS</t>
   </si>
   <si>
@@ -127,7 +127,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -804,10 +804,10 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="23" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="78.28515625" style="23" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="90.28515625" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.85546875" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="19.5703125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="12.28515625" style="23" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="12.42578125" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="6" max="6" width="38.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="7" max="7" width="11.7109375" style="23" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="8" max="8" width="27.140625" style="23" bestFit="1" customWidth="1" collapsed="1"/>
@@ -894,10 +894,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="12">
-        <v>217860.55</v>
+        <v>335867.81</v>
       </c>
       <c r="G5" s="13">
-        <v>0.96147625919589996</v>
+        <v>0.96788187847770002</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>12</v>
@@ -917,13 +917,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="17">
-        <v>60126702.828000002</v>
+        <v>66871917.171999998</v>
       </c>
       <c r="F6" s="18">
-        <v>80076.740000000005</v>
+        <v>100013.64</v>
       </c>
       <c r="G6" s="19">
-        <v>0.35339984418390002</v>
+        <v>0.28821276369600002</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>12</v>
@@ -946,10 +946,10 @@
         <v>175997197.75799999</v>
       </c>
       <c r="F7" s="18">
-        <v>45512.88</v>
+        <v>46533.66</v>
       </c>
       <c r="G7" s="19">
-        <v>0.20086038343170001</v>
+        <v>0.13409765661449999</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>12</v>
@@ -969,13 +969,13 @@
         <v>15</v>
       </c>
       <c r="E8" s="17">
-        <v>101389016.35699999</v>
+        <v>109249617.414</v>
       </c>
       <c r="F8" s="18">
-        <v>40403.519999999997</v>
+        <v>45305.82</v>
       </c>
       <c r="G8" s="19">
-        <v>0.1783114256709</v>
+        <v>0.1305593476421</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>12</v>
@@ -995,13 +995,13 @@
         <v>15</v>
       </c>
       <c r="E9" s="17">
-        <v>7252998.9220000003</v>
+        <v>17830515.192000002</v>
       </c>
       <c r="F9" s="18">
-        <v>14052.69</v>
+        <v>39052.39</v>
       </c>
       <c r="G9" s="19">
-        <v>6.2018239708099998E-2</v>
+        <v>0.1125386222402</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>12</v>
@@ -1021,13 +1021,13 @@
         <v>15</v>
       </c>
       <c r="E10" s="17">
-        <v>132639495.046</v>
+        <v>111466833.29000001</v>
       </c>
       <c r="F10" s="18">
-        <v>13078.25</v>
+        <v>33210.65</v>
       </c>
       <c r="G10" s="19">
-        <v>5.7717778123800002E-2</v>
+        <v>9.5704278142799998E-2</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>12</v>
@@ -1047,13 +1047,13 @@
         <v>15</v>
       </c>
       <c r="E11" s="17">
-        <v>34899152.560999997</v>
+        <v>320961647.62099999</v>
       </c>
       <c r="F11" s="18">
-        <v>10108.09</v>
+        <v>32577.61</v>
       </c>
       <c r="G11" s="19">
-        <v>4.4609676055700001E-2</v>
+        <v>9.3880024891699998E-2</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>12</v>
@@ -1073,13 +1073,13 @@
         <v>15</v>
       </c>
       <c r="E12" s="17">
-        <v>52563084.703000002</v>
+        <v>4823768.2309999997</v>
       </c>
       <c r="F12" s="18">
-        <v>8625.6</v>
+        <v>25313.21</v>
       </c>
       <c r="G12" s="19">
-        <v>3.8067055377000003E-2</v>
+        <v>7.29459522932E-2</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>12</v>
@@ -1099,13 +1099,13 @@
         <v>15</v>
       </c>
       <c r="E13" s="17">
-        <v>1138356.075</v>
+        <v>132639495.046</v>
       </c>
       <c r="F13" s="18">
-        <v>6002.78</v>
+        <v>13860.83</v>
       </c>
       <c r="G13" s="19">
-        <v>2.6491856644799999E-2</v>
+        <v>3.9943232957200002E-2</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>12</v>
@@ -1136,10 +1136,10 @@
         <v>12</v>
       </c>
       <c r="F15" s="12">
-        <v>9291.7900000000009</v>
+        <v>11124.98</v>
       </c>
       <c r="G15" s="13">
-        <v>4.1007128139699998E-2</v>
+        <v>3.2059239438299997E-2</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>12</v>
@@ -1170,10 +1170,10 @@
         <v>12</v>
       </c>
       <c r="F17" s="21">
-        <v>-562.70981808000943</v>
+        <v>20.432861589943059</v>
       </c>
       <c r="G17" s="22">
-        <v>-2.4833873360763756E-3</v>
+        <v>5.8882083574356843E-5</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>12</v>
@@ -1196,10 +1196,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="21">
-        <v>226589.63018191999</v>
+        <v>347013.22286158998</v>
       </c>
       <c r="G18" s="22">
-        <v>0.99999999999952371</v>
+        <v>0.99999999999957456</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>12</v>
